--- a/DATA/MASTER/C10_MASTER/Perfil_general_Dataset_Maestro_Framework_v04.xlsx
+++ b/DATA/MASTER/C10_MASTER/Perfil_general_Dataset_Maestro_Framework_v04.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68.16</v>
+        <v>73.59</v>
       </c>
     </row>
   </sheetData>
